--- a/data/data_chuqui_3mb_onboard_variable/elmo_data.xlsx
+++ b/data/data_chuqui_3mb_onboard_variable/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\data_chuqui_3mb_onboard_variable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34617803-85D9-4E02-83D8-BCBD487ACCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E78D85C-36AF-4C41-82BE-6D1909EDC00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batteries" sheetId="1" r:id="rId1"/>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
